--- a/output/pdf_financials_xlsx/NTH.xlsx
+++ b/output/pdf_financials_xlsx/NTH.xlsx
@@ -1308,19 +1308,19 @@
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.305065</v>
+        <v>-0.305065</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.516326</v>
+        <v>-0.516326</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.557459</v>
+        <v>-0.557459</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>3.966947</v>
+        <v>-3.966947</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>6.685952</v>
+        <v>-6.685952</v>
       </c>
       <c r="L16" s="3" t="n">
         <v>-4.920525</v>
@@ -1612,19 +1612,19 @@
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.305065</v>
+        <v>-0.305065</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.516326</v>
+        <v>-0.516326</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.557459</v>
+        <v>-0.557459</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>3.966947</v>
+        <v>-3.966947</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>6.685952</v>
+        <v>-6.685952</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>-4.920525</v>
@@ -1792,19 +1792,19 @@
         </is>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.305065</v>
+        <v>-0.305065</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.516326</v>
+        <v>-0.516326</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.557459</v>
+        <v>-0.557459</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>3.966947</v>
+        <v>-3.966947</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>6.685952</v>
+        <v>-6.685952</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>-4.920525</v>
@@ -1996,19 +1996,19 @@
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>15.25325</v>
+        <v>-15.25325</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>25.8163</v>
+        <v>-25.8163</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>27.87295</v>
+        <v>-27.87295</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>44.077189</v>
+        <v>-44.077189</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>66.85952</v>
+        <v>-66.85952</v>
       </c>
       <c r="L26" s="3" t="n">
         <v>82.00875000000001</v>
@@ -2056,19 +2056,19 @@
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.305065</v>
+        <v>-0.305065</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.516326</v>
+        <v>-0.516326</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.557459</v>
+        <v>-0.557459</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>3.966947</v>
+        <v>-3.966947</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>6.685952</v>
+        <v>-6.685952</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>-4.920525</v>
@@ -2176,19 +2176,19 @@
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.305065</v>
+        <v>-0.305065</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.516326</v>
+        <v>-0.516326</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.557459</v>
+        <v>-0.557459</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>3.966947</v>
+        <v>-3.966947</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>6.72537</v>
+        <v>-6.646534</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>-4.848691</v>
@@ -2326,19 +2326,19 @@
         </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
         <v>-0</v>
@@ -5964,7 +5964,7 @@
         <v>0.93445</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>1.827429</v>
+        <v>3.700704</v>
       </c>
       <c r="E92" s="3" t="n">
         <v>3.704717</v>
@@ -5979,34 +5979,34 @@
         <v>3.710157</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>3.72415</v>
+        <v>3.919076</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>3.739815</v>
+        <v>6.119758</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>4.032972</v>
+        <v>7.342916</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>4.456096</v>
+        <v>8.282005</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>4.844479</v>
+        <v>13.189806</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>5.480966</v>
+        <v>15.89487</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>6.62026</v>
+        <v>17.781678</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>9.545825000000001</v>
+        <v>18.337817</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>12.390457</v>
+        <v>18.427203</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>17.919506</v>
+        <v>25.455708</v>
       </c>
     </row>
     <row r="93">
@@ -10143,7 +10143,11 @@
           <t>Reserves (Note 10)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -12228,7 +12232,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
@@ -13533,7 +13541,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
@@ -14600,7 +14612,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -15598,7 +15614,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>-</t>
@@ -17000,7 +17020,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
           <t>-</t>
@@ -21052,7 +21076,11 @@
           <t>Warrants reserve (note 9(c))</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E125" t="inlineStr">
         <is>
           <t>-</t>
@@ -53614,10 +53642,10 @@
         </is>
       </c>
       <c r="N452" s="5" t="n">
-        <v>6.685952</v>
+        <v>-6.685952</v>
       </c>
       <c r="O452" s="5" t="n">
-        <v>4.920525</v>
+        <v>-4.920525</v>
       </c>
       <c r="P452" t="inlineStr">
         <is>
@@ -54885,19 +54913,19 @@
         </is>
       </c>
       <c r="J465" s="5" t="n">
-        <v>0.305065</v>
+        <v>-0.305065</v>
       </c>
       <c r="K465" s="5" t="n">
-        <v>0.516326</v>
+        <v>-0.516326</v>
       </c>
       <c r="L465" s="5" t="n">
-        <v>0.557459</v>
+        <v>-0.557459</v>
       </c>
       <c r="M465" s="5" t="n">
-        <v>3.966947</v>
+        <v>-3.966947</v>
       </c>
       <c r="N465" s="5" t="n">
-        <v>6.685952</v>
+        <v>-6.685952</v>
       </c>
       <c r="O465" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/NTH.xlsx
+++ b/output/pdf_financials_xlsx/NTH.xlsx
@@ -961,22 +961,22 @@
         <v>0.244589</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.014223</v>
+        <v>4.920525</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.078776</v>
+        <v>10.955686</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.319109</v>
+        <v>16.413314</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.136256</v>
+        <v>11.268645</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.419161</v>
+        <v>6.065416</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.96582</v>
+        <v>2.610683</v>
       </c>
       <c r="R10" s="3" t="n">
         <v>1.332159</v>
@@ -1021,19 +1021,19 @@
         <v>-0.244589</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-0.014223</v>
+        <v>-4.920525</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-0.078776</v>
+        <v>-10.955686</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>-0.319109</v>
+        <v>-16.413314</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>-0.136256</v>
+        <v>-11.268645</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-0.419161</v>
+        <v>-6.065416</v>
       </c>
       <c r="Q11" s="1" t="inlineStr">
         <is>
@@ -1054,13 +1054,13 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.017346</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.024574</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.002166</v>
       </c>
       <c r="F12" s="1" t="inlineStr">
         <is>
@@ -2042,13 +2042,13 @@
         <v>-1.402014</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-3.13226</v>
+        <v>-3.149606</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-8.326930000000001</v>
+        <v>-8.351504</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.819972</v>
+        <v>-1.822138</v>
       </c>
       <c r="F27" s="1" t="inlineStr">
         <is>
@@ -2162,13 +2162,13 @@
         <v>-1.402014</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-3.112094</v>
+        <v>-3.12944</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-8.280381</v>
+        <v>-8.304955</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.819972</v>
+        <v>-1.822138</v>
       </c>
       <c r="F29" s="1" t="inlineStr">
         <is>
@@ -2484,37 +2484,37 @@
         <v>0.003257</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.000139</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.00317</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.446897</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.281659</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.685715</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>6.421345</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>4.217908</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.323635</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.245827</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.001989</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>2.722617</v>
       </c>
     </row>
     <row r="35">
@@ -2600,37 +2600,37 @@
         <v>0.003257</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.000139</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.00317</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.446897</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.281659</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.685715</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>6.421345</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.91632</v>
+        <v>5.134228</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.327325</v>
+        <v>0.65096</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.205395</v>
+        <v>0.451222</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0.56868</v>
+        <v>0.570669</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0.946133</v>
+        <v>3.66875</v>
       </c>
     </row>
     <row r="37">
@@ -3302,31 +3302,31 @@
         <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.582082</v>
+        <v>0.135185</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.281659</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.735715</v>
+        <v>0.05</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>6.540977</v>
+        <v>0.119632</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>4.633552</v>
+        <v>0.415644</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.128897</v>
+        <v>0</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.605487</v>
+        <v>0.35966</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.351759</v>
+        <v>0.34977</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>3.480025</v>
+        <v>0.757408</v>
       </c>
     </row>
     <row r="49">
@@ -8917,7 +8917,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -14717,7 +14717,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -47909,7 +47909,7 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
@@ -57995,7 +57995,7 @@
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E496" t="inlineStr">
